--- a/se qb.xlsx
+++ b/se qb.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harsh\OneDrive\Desktop\SEM VI\SE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meeth\OneDrive\Desktop\Projects\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FCA6F4-0BDE-4DF7-9F64-6D08B0B93BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239FA3D4-3F60-4C96-8EE8-AB837E19D801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2202,22 +2202,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA305"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="91.109375" customWidth="1"/>
-    <col min="2" max="2" width="217.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="43.44140625" customWidth="1"/>
-    <col min="5" max="5" width="70.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="91.140625" customWidth="1"/>
+    <col min="2" max="2" width="217.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="43.42578125" customWidth="1"/>
+    <col min="5" max="5" width="70.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="24.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="83"/>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -2246,7 +2246,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="104"/>
       <c r="B2" s="105"/>
       <c r="C2" s="105"/>
@@ -2275,7 +2275,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="104"/>
       <c r="B3" s="105"/>
       <c r="C3" s="105"/>
@@ -2304,7 +2304,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="104"/>
       <c r="B4" s="105"/>
       <c r="C4" s="105"/>
@@ -2333,7 +2333,7 @@
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="107"/>
       <c r="B5" s="108"/>
       <c r="C5" s="108"/>
@@ -2362,7 +2362,7 @@
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
     </row>
-    <row r="6" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2391,7 +2391,7 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
     </row>
-    <row r="7" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
     </row>
-    <row r="8" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2457,7 +2457,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2494,7 +2494,7 @@
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2523,7 +2523,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2585,7 +2585,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="90"/>
       <c r="B13" s="112"/>
       <c r="C13" s="112"/>
@@ -2614,7 +2614,7 @@
       <c r="Z13" s="45"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="116"/>
       <c r="B14" s="105"/>
       <c r="C14" s="105"/>
@@ -2643,7 +2643,7 @@
       <c r="Z14" s="45"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="116"/>
       <c r="B15" s="105"/>
       <c r="C15" s="105"/>
@@ -2672,7 +2672,7 @@
       <c r="Z15" s="45"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="116"/>
       <c r="B16" s="105"/>
       <c r="C16" s="105"/>
@@ -2701,7 +2701,7 @@
       <c r="Z16" s="45"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="119"/>
       <c r="B17" s="120"/>
       <c r="C17" s="120"/>
@@ -2730,7 +2730,7 @@
       <c r="Z17" s="45"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45"/>
       <c r="B18" s="39"/>
       <c r="C18" s="45"/>
@@ -2759,7 +2759,7 @@
       <c r="Z18" s="45"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" ht="65.400000000000006" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:27" ht="66.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="65" t="s">
         <v>0</v>
       </c>
@@ -2793,7 +2793,7 @@
       <c r="Z19" s="45"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" ht="33" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:27" ht="33.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="65" t="s">
         <v>4</v>
       </c>
@@ -2830,7 +2830,7 @@
       <c r="Z20" s="45"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="61.8" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:27" ht="62.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="65" t="s">
         <v>14</v>
       </c>
@@ -2871,7 +2871,7 @@
       <c r="Z21" s="45"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" ht="33" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:27" ht="33.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="65" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2904,7 @@
       <c r="Z22" s="45"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="66" x14ac:dyDescent="0.25">
       <c r="A23" s="91" t="s">
         <v>21</v>
       </c>
@@ -2937,7 +2937,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="100"/>
       <c r="B24" s="78"/>
       <c r="C24" s="129"/>
@@ -2966,7 +2966,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="101"/>
       <c r="B25" s="78"/>
       <c r="C25" s="129"/>
@@ -2995,7 +2995,7 @@
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>23</v>
       </c>
@@ -3040,7 +3040,7 @@
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>1</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>2</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
     </row>
-    <row r="29" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>3</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>4</v>
       </c>
@@ -3246,7 +3246,7 @@
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
     </row>
-    <row r="31" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>5</v>
       </c>
@@ -3299,7 +3299,7 @@
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
     </row>
-    <row r="32" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>6</v>
       </c>
@@ -3352,7 +3352,7 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>7</v>
       </c>
@@ -3405,7 +3405,7 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>8</v>
       </c>
@@ -3458,7 +3458,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:27" ht="53.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>9</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="1:27" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:27" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>10</v>
       </c>
@@ -3550,7 +3550,7 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A37" s="20">
         <v>11</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>12</v>
       </c>
@@ -3656,7 +3656,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>13</v>
       </c>
@@ -3709,7 +3709,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>14</v>
       </c>
@@ -3762,7 +3762,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A41" s="20">
         <v>15</v>
       </c>
@@ -3815,7 +3815,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>16</v>
       </c>
@@ -3868,7 +3868,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>17</v>
       </c>
@@ -3921,7 +3921,7 @@
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>18</v>
       </c>
@@ -3966,7 +3966,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:27" ht="53.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20">
         <v>19</v>
       </c>
@@ -4011,7 +4011,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:27" ht="53.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
         <v>20</v>
       </c>
@@ -4056,7 +4056,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:27" ht="53.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14">
         <v>21</v>
       </c>
@@ -4101,7 +4101,7 @@
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="1:27" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="66" x14ac:dyDescent="0.25">
       <c r="A48" s="91" t="s">
         <v>90</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="100"/>
       <c r="B49" s="78"/>
       <c r="C49" s="129"/>
@@ -4163,7 +4163,7 @@
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="50" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A50" s="101"/>
       <c r="B50" s="95"/>
       <c r="C50" s="129"/>
@@ -4192,7 +4192,7 @@
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
     </row>
-    <row r="51" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>22</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>23</v>
       </c>
@@ -4282,7 +4282,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>24</v>
       </c>
@@ -4327,7 +4327,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>25</v>
       </c>
@@ -4372,7 +4372,7 @@
       <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
     </row>
-    <row r="55" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>26</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>27</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>28</v>
       </c>
@@ -4507,7 +4507,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>29</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>30</v>
       </c>
@@ -4597,7 +4597,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>31</v>
       </c>
@@ -4642,7 +4642,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>32</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>33</v>
       </c>
@@ -4732,7 +4732,7 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>34</v>
       </c>
@@ -4777,7 +4777,7 @@
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>35</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
     </row>
-    <row r="65" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>36</v>
       </c>
@@ -4867,7 +4867,7 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>37</v>
       </c>
@@ -4912,7 +4912,7 @@
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
     </row>
-    <row r="67" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>38</v>
       </c>
@@ -4957,7 +4957,7 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>39</v>
       </c>
@@ -5002,7 +5002,7 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>40</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>41</v>
       </c>
@@ -5092,7 +5092,7 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>42</v>
       </c>
@@ -5137,7 +5137,7 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" ht="66" x14ac:dyDescent="0.25">
       <c r="A72" s="91" t="s">
         <v>120</v>
       </c>
@@ -5170,7 +5170,7 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A73" s="100"/>
       <c r="B73" s="78"/>
       <c r="C73" s="129"/>
@@ -5199,7 +5199,7 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A74" s="101"/>
       <c r="B74" s="78"/>
       <c r="C74" s="129"/>
@@ -5228,7 +5228,7 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>43</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="Z75" s="7"/>
       <c r="AA75" s="7"/>
     </row>
-    <row r="76" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>44</v>
       </c>
@@ -5318,7 +5318,7 @@
       <c r="Z76" s="7"/>
       <c r="AA76" s="7"/>
     </row>
-    <row r="77" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>45</v>
       </c>
@@ -5363,7 +5363,7 @@
       <c r="Z77" s="7"/>
       <c r="AA77" s="7"/>
     </row>
-    <row r="78" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>46</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="Z78" s="7"/>
       <c r="AA78" s="7"/>
     </row>
-    <row r="79" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>47</v>
       </c>
@@ -5453,7 +5453,7 @@
       <c r="Z79" s="7"/>
       <c r="AA79" s="7"/>
     </row>
-    <row r="80" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>48</v>
       </c>
@@ -5498,7 +5498,7 @@
       <c r="Z80" s="7"/>
       <c r="AA80" s="7"/>
     </row>
-    <row r="81" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A81" s="14">
         <v>49</v>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="Z81" s="7"/>
       <c r="AA81" s="7"/>
     </row>
-    <row r="82" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A82" s="14">
         <v>50</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="Z82" s="7"/>
       <c r="AA82" s="7"/>
     </row>
-    <row r="83" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A83" s="14">
         <v>51</v>
       </c>
@@ -5633,7 +5633,7 @@
       <c r="Z83" s="7"/>
       <c r="AA83" s="7"/>
     </row>
-    <row r="84" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A84" s="14">
         <v>52</v>
       </c>
@@ -5678,7 +5678,7 @@
       <c r="Z84" s="7"/>
       <c r="AA84" s="7"/>
     </row>
-    <row r="85" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A85" s="14">
         <v>53</v>
       </c>
@@ -5723,7 +5723,7 @@
       <c r="Z85" s="7"/>
       <c r="AA85" s="7"/>
     </row>
-    <row r="86" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A86" s="14">
         <v>54</v>
       </c>
@@ -5768,7 +5768,7 @@
       <c r="Z86" s="7"/>
       <c r="AA86" s="7"/>
     </row>
-    <row r="87" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A87" s="14">
         <v>55</v>
       </c>
@@ -5813,7 +5813,7 @@
       <c r="Z87" s="7"/>
       <c r="AA87" s="7"/>
     </row>
-    <row r="88" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A88" s="14">
         <v>56</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="Z88" s="7"/>
       <c r="AA88" s="7"/>
     </row>
-    <row r="89" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A89" s="14">
         <v>57</v>
       </c>
@@ -5903,7 +5903,7 @@
       <c r="Z89" s="7"/>
       <c r="AA89" s="7"/>
     </row>
-    <row r="90" spans="1:27" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A90" s="24">
         <v>58</v>
       </c>
@@ -5948,7 +5948,7 @@
       <c r="Z90" s="8"/>
       <c r="AA90" s="8"/>
     </row>
-    <row r="91" spans="1:27" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A91" s="73">
         <v>59</v>
       </c>
@@ -5993,7 +5993,7 @@
       <c r="Z91" s="8"/>
       <c r="AA91" s="8"/>
     </row>
-    <row r="92" spans="1:27" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A92" s="24">
         <v>60</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="Z92" s="8"/>
       <c r="AA92" s="8"/>
     </row>
-    <row r="93" spans="1:27" ht="136.80000000000001" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" ht="139.5" x14ac:dyDescent="0.25">
       <c r="A93" s="24">
         <v>61</v>
       </c>
@@ -6083,7 +6083,7 @@
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
     </row>
-    <row r="94" spans="1:27" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" ht="93" x14ac:dyDescent="0.25">
       <c r="A94" s="24">
         <v>62</v>
       </c>
@@ -6128,7 +6128,7 @@
       <c r="Z94" s="8"/>
       <c r="AA94" s="8"/>
     </row>
-    <row r="95" spans="1:27" ht="205.2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" ht="209.25" x14ac:dyDescent="0.25">
       <c r="A95" s="24">
         <v>63</v>
       </c>
@@ -6173,7 +6173,7 @@
       <c r="Z95" s="8"/>
       <c r="AA95" s="8"/>
     </row>
-    <row r="96" spans="1:27" ht="63.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" ht="66" x14ac:dyDescent="0.25">
       <c r="A96" s="99" t="s">
         <v>153</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
     </row>
-    <row r="97" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A97" s="100"/>
       <c r="B97" s="78"/>
       <c r="C97" s="137"/>
@@ -6235,7 +6235,7 @@
       <c r="Z97" s="2"/>
       <c r="AA97" s="2"/>
     </row>
-    <row r="98" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A98" s="101"/>
       <c r="B98" s="78"/>
       <c r="C98" s="129"/>
@@ -6264,7 +6264,7 @@
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
     </row>
-    <row r="99" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A99" s="14">
         <v>64</v>
       </c>
@@ -6309,7 +6309,7 @@
       <c r="Z99" s="7"/>
       <c r="AA99" s="7"/>
     </row>
-    <row r="100" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A100" s="14">
         <v>65</v>
       </c>
@@ -6354,7 +6354,7 @@
       <c r="Z100" s="7"/>
       <c r="AA100" s="7"/>
     </row>
-    <row r="101" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A101" s="14">
         <v>66</v>
       </c>
@@ -6399,7 +6399,7 @@
       <c r="Z101" s="7"/>
       <c r="AA101" s="7"/>
     </row>
-    <row r="102" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A102" s="14">
         <v>67</v>
       </c>
@@ -6444,7 +6444,7 @@
       <c r="Z102" s="7"/>
       <c r="AA102" s="7"/>
     </row>
-    <row r="103" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A103" s="14">
         <v>68</v>
       </c>
@@ -6489,7 +6489,7 @@
       <c r="Z103" s="7"/>
       <c r="AA103" s="7"/>
     </row>
-    <row r="104" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A104" s="14">
         <v>69</v>
       </c>
@@ -6534,7 +6534,7 @@
       <c r="Z104" s="7"/>
       <c r="AA104" s="7"/>
     </row>
-    <row r="105" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A105" s="14">
         <v>70</v>
       </c>
@@ -6579,7 +6579,7 @@
       <c r="Z105" s="7"/>
       <c r="AA105" s="7"/>
     </row>
-    <row r="106" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A106" s="14">
         <v>71</v>
       </c>
@@ -6624,7 +6624,7 @@
       <c r="Z106" s="7"/>
       <c r="AA106" s="7"/>
     </row>
-    <row r="107" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A107" s="14">
         <v>72</v>
       </c>
@@ -6669,7 +6669,7 @@
       <c r="Z107" s="7"/>
       <c r="AA107" s="7"/>
     </row>
-    <row r="108" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A108" s="14">
         <v>73</v>
       </c>
@@ -6714,7 +6714,7 @@
       <c r="Z108" s="7"/>
       <c r="AA108" s="7"/>
     </row>
-    <row r="109" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A109" s="14">
         <v>74</v>
       </c>
@@ -6759,7 +6759,7 @@
       <c r="Z109" s="7"/>
       <c r="AA109" s="7"/>
     </row>
-    <row r="110" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A110" s="14">
         <v>75</v>
       </c>
@@ -6804,7 +6804,7 @@
       <c r="Z110" s="7"/>
       <c r="AA110" s="7"/>
     </row>
-    <row r="111" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A111" s="14">
         <v>76</v>
       </c>
@@ -6849,7 +6849,7 @@
       <c r="Z111" s="7"/>
       <c r="AA111" s="7"/>
     </row>
-    <row r="112" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A112" s="14">
         <v>77</v>
       </c>
@@ -6894,7 +6894,7 @@
       <c r="Z112" s="7"/>
       <c r="AA112" s="7"/>
     </row>
-    <row r="113" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A113" s="14">
         <v>78</v>
       </c>
@@ -6939,7 +6939,7 @@
       <c r="Z113" s="7"/>
       <c r="AA113" s="7"/>
     </row>
-    <row r="114" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A114" s="14">
         <v>79</v>
       </c>
@@ -6984,7 +6984,7 @@
       <c r="Z114" s="7"/>
       <c r="AA114" s="7"/>
     </row>
-    <row r="115" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A115" s="14">
         <v>80</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="Z115" s="7"/>
       <c r="AA115" s="7"/>
     </row>
-    <row r="116" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
         <v>81</v>
       </c>
@@ -7074,7 +7074,7 @@
       <c r="Z116" s="7"/>
       <c r="AA116" s="7"/>
     </row>
-    <row r="117" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>82</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="Z117" s="7"/>
       <c r="AA117" s="7"/>
     </row>
-    <row r="118" spans="1:27" ht="169.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" ht="166.5" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>83</v>
       </c>
@@ -7164,7 +7164,7 @@
       <c r="Z118" s="7"/>
       <c r="AA118" s="7"/>
     </row>
-    <row r="119" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A119" s="53">
         <v>84</v>
       </c>
@@ -7209,7 +7209,7 @@
       <c r="Z119" s="7"/>
       <c r="AA119" s="7"/>
     </row>
-    <row r="120" spans="1:27" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" ht="99" x14ac:dyDescent="0.25">
       <c r="A120" s="91" t="s">
         <v>179</v>
       </c>
@@ -7242,7 +7242,7 @@
       <c r="Z120" s="7"/>
       <c r="AA120" s="7"/>
     </row>
-    <row r="121" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A121" s="100"/>
       <c r="B121" s="82"/>
       <c r="C121" s="129"/>
@@ -7271,7 +7271,7 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A122" s="101"/>
       <c r="B122" s="78"/>
       <c r="C122" s="129"/>
@@ -7300,7 +7300,7 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
         <v>85</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="Z123" s="7"/>
       <c r="AA123" s="7"/>
     </row>
-    <row r="124" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A124" s="14">
         <v>86</v>
       </c>
@@ -7390,7 +7390,7 @@
       <c r="Z124" s="7"/>
       <c r="AA124" s="7"/>
     </row>
-    <row r="125" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A125" s="14">
         <v>87</v>
       </c>
@@ -7435,7 +7435,7 @@
       <c r="Z125" s="7"/>
       <c r="AA125" s="7"/>
     </row>
-    <row r="126" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A126" s="14">
         <v>88</v>
       </c>
@@ -7480,7 +7480,7 @@
       <c r="Z126" s="7"/>
       <c r="AA126" s="7"/>
     </row>
-    <row r="127" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A127" s="14">
         <v>89</v>
       </c>
@@ -7525,7 +7525,7 @@
       <c r="Z127" s="7"/>
       <c r="AA127" s="7"/>
     </row>
-    <row r="128" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A128" s="14">
         <v>90</v>
       </c>
@@ -7570,7 +7570,7 @@
       <c r="Z128" s="7"/>
       <c r="AA128" s="7"/>
     </row>
-    <row r="129" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A129" s="14">
         <v>91</v>
       </c>
@@ -7615,7 +7615,7 @@
       <c r="Z129" s="7"/>
       <c r="AA129" s="7"/>
     </row>
-    <row r="130" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A130" s="14">
         <v>92</v>
       </c>
@@ -7660,7 +7660,7 @@
       <c r="Z130" s="7"/>
       <c r="AA130" s="7"/>
     </row>
-    <row r="131" spans="1:27" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A131" s="14">
         <v>93</v>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="Z131" s="7"/>
       <c r="AA131" s="7"/>
     </row>
-    <row r="132" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A132" s="14">
         <v>94</v>
       </c>
@@ -7750,7 +7750,7 @@
       <c r="Z132" s="7"/>
       <c r="AA132" s="7"/>
     </row>
-    <row r="133" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A133" s="14">
         <v>95</v>
       </c>
@@ -7795,7 +7795,7 @@
       <c r="Z133" s="7"/>
       <c r="AA133" s="7"/>
     </row>
-    <row r="134" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A134" s="14">
         <v>96</v>
       </c>
@@ -7840,7 +7840,7 @@
       <c r="Z134" s="7"/>
       <c r="AA134" s="7"/>
     </row>
-    <row r="135" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A135" s="14">
         <v>97</v>
       </c>
@@ -7885,7 +7885,7 @@
       <c r="Z135" s="7"/>
       <c r="AA135" s="7"/>
     </row>
-    <row r="136" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A136" s="14">
         <v>98</v>
       </c>
@@ -7930,7 +7930,7 @@
       <c r="Z136" s="7"/>
       <c r="AA136" s="7"/>
     </row>
-    <row r="137" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A137" s="14">
         <v>99</v>
       </c>
@@ -7975,7 +7975,7 @@
       <c r="Z137" s="7"/>
       <c r="AA137" s="7"/>
     </row>
-    <row r="138" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A138" s="14">
         <v>100</v>
       </c>
@@ -8020,7 +8020,7 @@
       <c r="Z138" s="7"/>
       <c r="AA138" s="7"/>
     </row>
-    <row r="139" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A139" s="14">
         <v>101</v>
       </c>
@@ -8065,7 +8065,7 @@
       <c r="Z139" s="7"/>
       <c r="AA139" s="7"/>
     </row>
-    <row r="140" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
         <v>102</v>
       </c>
@@ -8110,7 +8110,7 @@
       <c r="Z140" s="7"/>
       <c r="AA140" s="7"/>
     </row>
-    <row r="141" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>103</v>
       </c>
@@ -8155,7 +8155,7 @@
       <c r="Z141" s="7"/>
       <c r="AA141" s="7"/>
     </row>
-    <row r="142" spans="1:27" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A142" s="53">
         <v>104</v>
       </c>
@@ -8200,7 +8200,7 @@
       <c r="Z142" s="7"/>
       <c r="AA142" s="7"/>
     </row>
-    <row r="143" spans="1:27" ht="253.8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" ht="249.75" x14ac:dyDescent="0.25">
       <c r="A143" s="60">
         <v>105</v>
       </c>
@@ -8245,7 +8245,7 @@
       <c r="Z143" s="7"/>
       <c r="AA143" s="7"/>
     </row>
-    <row r="144" spans="1:27" ht="197.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" ht="194.25" x14ac:dyDescent="0.25">
       <c r="A144" s="57">
         <v>106</v>
       </c>
@@ -8290,7 +8290,7 @@
       <c r="Z144" s="7"/>
       <c r="AA144" s="7"/>
     </row>
-    <row r="145" spans="1:27" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" ht="66" x14ac:dyDescent="0.25">
       <c r="A145" s="98" t="s">
         <v>205</v>
       </c>
@@ -8323,7 +8323,7 @@
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
     </row>
-    <row r="146" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A146" s="100"/>
       <c r="B146" s="78"/>
       <c r="C146" s="129"/>
@@ -8352,7 +8352,7 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A147" s="101"/>
       <c r="B147" s="78"/>
       <c r="C147" s="129"/>
@@ -8381,7 +8381,7 @@
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
     </row>
-    <row r="148" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A148" s="24">
         <v>107</v>
       </c>
@@ -8426,7 +8426,7 @@
       <c r="Z148" s="8"/>
       <c r="AA148" s="8"/>
     </row>
-    <row r="149" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A149" s="24">
         <v>108</v>
       </c>
@@ -8471,7 +8471,7 @@
       <c r="Z149" s="8"/>
       <c r="AA149" s="8"/>
     </row>
-    <row r="150" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A150" s="24">
         <v>109</v>
       </c>
@@ -8516,7 +8516,7 @@
       <c r="Z150" s="8"/>
       <c r="AA150" s="8"/>
     </row>
-    <row r="151" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A151" s="24">
         <v>110</v>
       </c>
@@ -8561,7 +8561,7 @@
       <c r="Z151" s="8"/>
       <c r="AA151" s="8"/>
     </row>
-    <row r="152" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A152" s="24">
         <v>111</v>
       </c>
@@ -8606,7 +8606,7 @@
       <c r="Z152" s="8"/>
       <c r="AA152" s="8"/>
     </row>
-    <row r="153" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A153" s="24">
         <v>112</v>
       </c>
@@ -8651,7 +8651,7 @@
       <c r="Z153" s="8"/>
       <c r="AA153" s="8"/>
     </row>
-    <row r="154" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A154" s="24">
         <v>113</v>
       </c>
@@ -8696,7 +8696,7 @@
       <c r="Z154" s="8"/>
       <c r="AA154" s="8"/>
     </row>
-    <row r="155" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A155" s="24">
         <v>114</v>
       </c>
@@ -8741,7 +8741,7 @@
       <c r="Z155" s="8"/>
       <c r="AA155" s="8"/>
     </row>
-    <row r="156" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A156" s="24">
         <v>115</v>
       </c>
@@ -8786,7 +8786,7 @@
       <c r="Z156" s="8"/>
       <c r="AA156" s="8"/>
     </row>
-    <row r="157" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A157" s="24">
         <v>116</v>
       </c>
@@ -8831,7 +8831,7 @@
       <c r="Z157" s="8"/>
       <c r="AA157" s="8"/>
     </row>
-    <row r="158" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A158" s="24">
         <v>117</v>
       </c>
@@ -8876,7 +8876,7 @@
       <c r="Z158" s="8"/>
       <c r="AA158" s="8"/>
     </row>
-    <row r="159" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A159" s="24">
         <v>118</v>
       </c>
@@ -8921,7 +8921,7 @@
       <c r="Z159" s="8"/>
       <c r="AA159" s="8"/>
     </row>
-    <row r="160" spans="1:27" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A160" s="24">
         <v>119</v>
       </c>
@@ -8966,7 +8966,7 @@
       <c r="Z160" s="8"/>
       <c r="AA160" s="8"/>
     </row>
-    <row r="161" spans="1:27" ht="378" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A161" s="24">
         <v>120</v>
       </c>
@@ -9011,7 +9011,7 @@
       <c r="Z161" s="8"/>
       <c r="AA161" s="8"/>
     </row>
-    <row r="162" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A162" s="24">
         <v>121</v>
       </c>
@@ -9056,7 +9056,7 @@
       <c r="Z162" s="8"/>
       <c r="AA162" s="8"/>
     </row>
-    <row r="163" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A163" s="24">
         <v>122</v>
       </c>
@@ -9101,7 +9101,7 @@
       <c r="Z163" s="8"/>
       <c r="AA163" s="8"/>
     </row>
-    <row r="164" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A164" s="24">
         <v>123</v>
       </c>
@@ -9146,7 +9146,7 @@
       <c r="Z164" s="8"/>
       <c r="AA164" s="8"/>
     </row>
-    <row r="165" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A165" s="24">
         <v>124</v>
       </c>
@@ -9191,7 +9191,7 @@
       <c r="Z165" s="8"/>
       <c r="AA165" s="8"/>
     </row>
-    <row r="166" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A166" s="24">
         <v>125</v>
       </c>
@@ -9236,7 +9236,7 @@
       <c r="Z166" s="8"/>
       <c r="AA166" s="8"/>
     </row>
-    <row r="167" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A167" s="24">
         <v>126</v>
       </c>
@@ -9281,7 +9281,7 @@
       <c r="Z167" s="8"/>
       <c r="AA167" s="8"/>
     </row>
-    <row r="168" spans="1:27" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A168" s="24">
         <v>127</v>
       </c>
@@ -9326,7 +9326,7 @@
       <c r="Z168" s="8"/>
       <c r="AA168" s="8"/>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9355,7 +9355,7 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9384,7 +9384,7 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9413,7 +9413,7 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9442,7 +9442,7 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9471,7 +9471,7 @@
       <c r="Z173" s="2"/>
       <c r="AA173" s="2"/>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9500,7 +9500,7 @@
       <c r="Z174" s="2"/>
       <c r="AA174" s="2"/>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9529,7 +9529,7 @@
       <c r="Z175" s="2"/>
       <c r="AA175" s="2"/>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9558,7 +9558,7 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9587,7 +9587,7 @@
       <c r="Z177" s="2"/>
       <c r="AA177" s="2"/>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9616,7 +9616,7 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9645,7 +9645,7 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9674,7 +9674,7 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9703,7 +9703,7 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9732,7 +9732,7 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9761,7 +9761,7 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9790,7 +9790,7 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9819,7 +9819,7 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9848,7 +9848,7 @@
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9877,7 +9877,7 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9906,7 +9906,7 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9935,7 +9935,7 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9964,7 +9964,7 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9993,7 +9993,7 @@
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -10022,7 +10022,7 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -10051,7 +10051,7 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -10080,7 +10080,7 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -10109,7 +10109,7 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -10138,7 +10138,7 @@
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -10167,7 +10167,7 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -10196,7 +10196,7 @@
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -10225,7 +10225,7 @@
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -10254,7 +10254,7 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -10283,7 +10283,7 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -10312,7 +10312,7 @@
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -10341,7 +10341,7 @@
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -10370,7 +10370,7 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -10399,7 +10399,7 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -10428,7 +10428,7 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -10457,7 +10457,7 @@
       <c r="Z207" s="2"/>
       <c r="AA207" s="2"/>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10486,7 +10486,7 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10515,7 +10515,7 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10544,7 +10544,7 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10573,7 +10573,7 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10602,7 +10602,7 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10631,7 +10631,7 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10660,7 +10660,7 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10689,7 +10689,7 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10718,7 +10718,7 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10747,7 +10747,7 @@
       <c r="Z217" s="2"/>
       <c r="AA217" s="2"/>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10776,7 +10776,7 @@
       <c r="Z218" s="2"/>
       <c r="AA218" s="2"/>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10805,7 +10805,7 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10834,7 +10834,7 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10863,7 +10863,7 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10892,7 +10892,7 @@
       <c r="Z222" s="2"/>
       <c r="AA222" s="2"/>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10921,7 +10921,7 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10950,7 +10950,7 @@
       <c r="Z224" s="2"/>
       <c r="AA224" s="2"/>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10979,7 +10979,7 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -11008,7 +11008,7 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -11037,7 +11037,7 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -11066,7 +11066,7 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -11095,7 +11095,7 @@
       <c r="Z229" s="2"/>
       <c r="AA229" s="2"/>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -11124,7 +11124,7 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -11153,7 +11153,7 @@
       <c r="Z231" s="2"/>
       <c r="AA231" s="2"/>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -11182,7 +11182,7 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -11211,7 +11211,7 @@
       <c r="Z233" s="2"/>
       <c r="AA233" s="2"/>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -11240,7 +11240,7 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -11269,7 +11269,7 @@
       <c r="Z235" s="2"/>
       <c r="AA235" s="2"/>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -11298,7 +11298,7 @@
       <c r="Z236" s="2"/>
       <c r="AA236" s="2"/>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -11327,7 +11327,7 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -11356,7 +11356,7 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -11385,7 +11385,7 @@
       <c r="Z239" s="2"/>
       <c r="AA239" s="2"/>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -11414,7 +11414,7 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -11443,7 +11443,7 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -11472,7 +11472,7 @@
       <c r="Z242" s="2"/>
       <c r="AA242" s="2"/>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -11501,7 +11501,7 @@
       <c r="Z243" s="2"/>
       <c r="AA243" s="2"/>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -11530,7 +11530,7 @@
       <c r="Z244" s="2"/>
       <c r="AA244" s="2"/>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -11559,7 +11559,7 @@
       <c r="Z245" s="2"/>
       <c r="AA245" s="2"/>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -11588,7 +11588,7 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -11617,7 +11617,7 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -11646,7 +11646,7 @@
       <c r="Z248" s="2"/>
       <c r="AA248" s="2"/>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -11675,7 +11675,7 @@
       <c r="Z249" s="2"/>
       <c r="AA249" s="2"/>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -11704,7 +11704,7 @@
       <c r="Z250" s="2"/>
       <c r="AA250" s="2"/>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -11733,7 +11733,7 @@
       <c r="Z251" s="2"/>
       <c r="AA251" s="2"/>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -11762,7 +11762,7 @@
       <c r="Z252" s="2"/>
       <c r="AA252" s="2"/>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -11791,7 +11791,7 @@
       <c r="Z253" s="2"/>
       <c r="AA253" s="2"/>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -11820,7 +11820,7 @@
       <c r="Z254" s="2"/>
       <c r="AA254" s="2"/>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -11849,7 +11849,7 @@
       <c r="Z255" s="2"/>
       <c r="AA255" s="2"/>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -11878,7 +11878,7 @@
       <c r="Z256" s="2"/>
       <c r="AA256" s="2"/>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -11907,7 +11907,7 @@
       <c r="Z257" s="2"/>
       <c r="AA257" s="2"/>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -11936,7 +11936,7 @@
       <c r="Z258" s="2"/>
       <c r="AA258" s="2"/>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -11965,7 +11965,7 @@
       <c r="Z259" s="2"/>
       <c r="AA259" s="2"/>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11994,7 +11994,7 @@
       <c r="Z260" s="2"/>
       <c r="AA260" s="2"/>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -12023,7 +12023,7 @@
       <c r="Z261" s="2"/>
       <c r="AA261" s="2"/>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -12052,7 +12052,7 @@
       <c r="Z262" s="2"/>
       <c r="AA262" s="2"/>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -12081,7 +12081,7 @@
       <c r="Z263" s="2"/>
       <c r="AA263" s="2"/>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -12110,7 +12110,7 @@
       <c r="Z264" s="2"/>
       <c r="AA264" s="2"/>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -12139,7 +12139,7 @@
       <c r="Z265" s="2"/>
       <c r="AA265" s="2"/>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -12168,7 +12168,7 @@
       <c r="Z266" s="2"/>
       <c r="AA266" s="2"/>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -12197,7 +12197,7 @@
       <c r="Z267" s="2"/>
       <c r="AA267" s="2"/>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -12226,7 +12226,7 @@
       <c r="Z268" s="2"/>
       <c r="AA268" s="2"/>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -12255,7 +12255,7 @@
       <c r="Z269" s="2"/>
       <c r="AA269" s="2"/>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -12284,7 +12284,7 @@
       <c r="Z270" s="2"/>
       <c r="AA270" s="2"/>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -12313,7 +12313,7 @@
       <c r="Z271" s="2"/>
       <c r="AA271" s="2"/>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -12342,7 +12342,7 @@
       <c r="Z272" s="2"/>
       <c r="AA272" s="2"/>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -12371,7 +12371,7 @@
       <c r="Z273" s="2"/>
       <c r="AA273" s="2"/>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -12400,7 +12400,7 @@
       <c r="Z274" s="2"/>
       <c r="AA274" s="2"/>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -12429,7 +12429,7 @@
       <c r="Z275" s="2"/>
       <c r="AA275" s="2"/>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -12458,7 +12458,7 @@
       <c r="Z276" s="2"/>
       <c r="AA276" s="2"/>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -12487,7 +12487,7 @@
       <c r="Z277" s="2"/>
       <c r="AA277" s="2"/>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -12516,7 +12516,7 @@
       <c r="Z278" s="2"/>
       <c r="AA278" s="2"/>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -12545,7 +12545,7 @@
       <c r="Z279" s="2"/>
       <c r="AA279" s="2"/>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -12574,7 +12574,7 @@
       <c r="Z280" s="2"/>
       <c r="AA280" s="2"/>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -12603,7 +12603,7 @@
       <c r="Z281" s="2"/>
       <c r="AA281" s="2"/>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -12632,7 +12632,7 @@
       <c r="Z282" s="2"/>
       <c r="AA282" s="2"/>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -12661,7 +12661,7 @@
       <c r="Z283" s="2"/>
       <c r="AA283" s="2"/>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -12690,7 +12690,7 @@
       <c r="Z284" s="2"/>
       <c r="AA284" s="2"/>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -12719,7 +12719,7 @@
       <c r="Z285" s="2"/>
       <c r="AA285" s="2"/>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -12748,7 +12748,7 @@
       <c r="Z286" s="2"/>
       <c r="AA286" s="2"/>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -12777,7 +12777,7 @@
       <c r="Z287" s="2"/>
       <c r="AA287" s="2"/>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -12806,7 +12806,7 @@
       <c r="Z288" s="2"/>
       <c r="AA288" s="2"/>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -12835,7 +12835,7 @@
       <c r="Z289" s="2"/>
       <c r="AA289" s="2"/>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -12864,7 +12864,7 @@
       <c r="Z290" s="2"/>
       <c r="AA290" s="2"/>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -12893,7 +12893,7 @@
       <c r="Z291" s="1"/>
       <c r="AA291" s="1"/>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -12922,7 +12922,7 @@
       <c r="Z292" s="1"/>
       <c r="AA292" s="1"/>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -12951,7 +12951,7 @@
       <c r="Z293" s="1"/>
       <c r="AA293" s="1"/>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -12980,7 +12980,7 @@
       <c r="Z294" s="1"/>
       <c r="AA294" s="1"/>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -13009,7 +13009,7 @@
       <c r="Z295" s="1"/>
       <c r="AA295" s="1"/>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -13038,7 +13038,7 @@
       <c r="Z296" s="1"/>
       <c r="AA296" s="1"/>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -13067,7 +13067,7 @@
       <c r="Z297" s="1"/>
       <c r="AA297" s="1"/>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -13096,7 +13096,7 @@
       <c r="Z298" s="1"/>
       <c r="AA298" s="1"/>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -13125,7 +13125,7 @@
       <c r="Z299" s="1"/>
       <c r="AA299" s="1"/>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -13154,7 +13154,7 @@
       <c r="Z300" s="1"/>
       <c r="AA300" s="1"/>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -13183,7 +13183,7 @@
       <c r="Z301" s="1"/>
       <c r="AA301" s="1"/>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -13212,7 +13212,7 @@
       <c r="Z302" s="1"/>
       <c r="AA302" s="1"/>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -13241,7 +13241,7 @@
       <c r="Z303" s="1"/>
       <c r="AA303" s="1"/>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -13270,7 +13270,7 @@
       <c r="Z304" s="1"/>
       <c r="AA304" s="1"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
